--- a/data/merged/2026-09-28/MERGED_JP_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_JP_Mite-Vacuum_2026-09-28.xlsx
@@ -7318,314 +7318,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7951,7 +7643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16148,48 +15840,56 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0CLKZM25S</t>
-        </is>
-      </c>
-      <c r="D35" s="12"/>
+          <t>B09WMDJ3R8</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 白色</t>
+        </is>
+      </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>品牌: Dyson | 特殊功能: 可清洗过滤器, 无绳, 紧凑型, 轻巧 | 筛选类型: 滤芯 | 推荐表面: 家具装饰品 | 电源: 电池供电</t>
+          <t>品牌: Raycop | 特殊功能: 紫外线 | 筛选类型: 墨盒 | 推荐表面: 地毯 | 电源: 有线电动</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>RAYCOP(レイコップ)</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0CLKZM25S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09WMDJ3R8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Dyson Micro Focus Clean</t>
+          <t>RAYCOP UV被褥清洁剂 VCEN-100 UV99.9%除菌 除病毒 杀死螨虫 拍打18,000次 (白色) 防螨</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>持续不变的吸力</t>
+          <t>使用紫外线灯可达到99.9%的除菌效果，可去除病毒。3分钟内可去除90%以上的家庭灰尘。
+从人体工学的角度设计了手柄的长度、粗细和位置，提高了握持性能。此外，通过调整重量平衡和降低主体高度以降低重心，实现了轻巧的操作性。这是雷科普史上最轻、最紧凑的“轻量化”设计。
+吸引范围扩大至165毫米，与LITE相比约扩大了20%。一次能吸尘的范围更广，短时间内高效清洁床上用品。
+新开发的“鳍打冲洗刷”在减少对床单织物的损伤的同时，还能牢牢抓住难以去除的头发和宠物的毛发。采用具有优异弹性和耐磨性的橡胶材料，每分钟敲打次数提高到18,000次。
+搭载了在空气净化器和洁净室中也使用的「HEPA(高效微粒空气) 过滤器」。保持排气的清洁，能够99.9%收集0.3微米的颗粒。* 采用全球通用100-120V插座。</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CLKZM25S?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41OndC98uCL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/316163kM7LL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0CLKZM25S</t>
+          <t>B0C4KPD9VD</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
@@ -16203,11 +15903,13 @@
         </is>
       </c>
       <c r="O35" s="13">
-        <v>202845</v>
-      </c>
-      <c r="P35" s="13"/>
+        <v>77371</v>
+      </c>
+      <c r="P35" s="13">
+        <v>-78324</v>
+      </c>
       <c r="Q35" s="14">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
@@ -16216,15 +15918,17 @@
       </c>
       <c r="S35" s="16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T35" s="13">
-        <v>3</v>
-      </c>
-      <c r="U35" s="14"/>
+        <v>13</v>
+      </c>
+      <c r="U35" s="14">
+        <v>0.14</v>
+      </c>
       <c r="V35" s="13">
-        <v>114000</v>
+        <v>111436</v>
       </c>
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
@@ -16232,35 +15936,37 @@
         <v>1</v>
       </c>
       <c r="Z35" s="13">
-        <v>37500</v>
+        <v>8572</v>
       </c>
       <c r="AA35" s="2"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="13"/>
       <c r="AD35" s="17">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="AE35" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF35" s="18">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AG35" s="19">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="13"/>
+        <v>0.15380000000000002</v>
+      </c>
+      <c r="AH35" s="13">
+        <v>532</v>
+      </c>
       <c r="AI35" s="14">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="11" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2022-03-29</t>
         </is>
       </c>
       <c r="AL35" s="17">
-        <v>1065</v>
+        <v>1643</v>
       </c>
       <c r="AM35" s="11" t="inlineStr">
         <is>
@@ -16270,13 +15976,15 @@
       <c r="AN35" s="11"/>
       <c r="AO35" s="11"/>
       <c r="AP35" s="13"/>
-      <c r="AQ35" s="17"/>
+      <c r="AQ35" s="17">
+        <v>10</v>
+      </c>
       <c r="AR35" s="17">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AS35" s="12" t="inlineStr">
         <is>
-          <t>Korin商店 古物商許可番号第801010002249号</t>
+          <t>モリハウス</t>
         </is>
       </c>
       <c r="AT35" s="11" t="inlineStr">
@@ -16284,11 +15992,19 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU35" s="11"/>
-      <c r="AV35" s="12"/>
+      <c r="AU35" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AV35" s="12" t="inlineStr">
+        <is>
+          <t>守口市竹町 大阪府 5700086 JP</t>
+        </is>
+      </c>
       <c r="AW35" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A96F6A3HJYHX0</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
         </is>
       </c>
       <c r="AX35" s="11"/>
@@ -16296,34 +16012,62 @@
       <c r="AZ35" s="11"/>
       <c r="BA35" s="11"/>
       <c r="BB35" s="11"/>
-      <c r="BC35" s="11"/>
-      <c r="BD35" s="11"/>
+      <c r="BC35" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD35" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="11"/>
-      <c r="BF35" s="11"/>
+      <c r="BF35" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG35" s="11"/>
       <c r="BH35" s="12"/>
       <c r="BI35" s="20"/>
       <c r="BJ35" s="20" t="inlineStr">
         <is>
-          <t>2.67 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK35" s="20" t="inlineStr">
-        <is>
-          <t>2.67 kg</t>
-        </is>
-      </c>
+          <t>1.9 千克</t>
+        </is>
+      </c>
+      <c r="BK35" s="20"/>
       <c r="BL35" s="20" t="inlineStr">
         <is>
-          <t>14.2長さ x 22.2幅 x 41.5高さ cm</t>
+          <t>37.1長さ x 29幅 x 14.9高さ cm</t>
         </is>
       </c>
       <c r="BM35" s="20"/>
-      <c r="BN35" s="20"/>
-      <c r="BO35" s="20"/>
-      <c r="BP35" s="20"/>
-      <c r="BQ35" s="20"/>
-      <c r="BR35" s="11"/>
+      <c r="BN35" s="20" t="inlineStr">
+        <is>
+          <t>3.52 kg</t>
+        </is>
+      </c>
+      <c r="BO35" s="20" t="inlineStr">
+        <is>
+          <t>3.52 kg</t>
+        </is>
+      </c>
+      <c r="BP35" s="20" t="inlineStr">
+        <is>
+          <t>41 x 31 x 19.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ35" s="20" t="inlineStr">
+        <is>
+          <t>41.00 x 31.00 x 19.50 cm</t>
+        </is>
+      </c>
+      <c r="BR35" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -16332,17 +16076,17 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B09WMDJ3R8</t>
+          <t>B08XM26HKK</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>颜色: 白色</t>
+          <t>样式: 1)被褥吸尘器</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>品牌: Raycop | 特殊功能: 紫外线 | 筛选类型: 墨盒 | 推荐表面: 地毯 | 电源: 有线电动</t>
+          <t>品牌: Raycop | 特殊功能: 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 被子 | 电源: 有线电动</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -16352,36 +16096,36 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09WMDJ3R8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP UV被褥清洁剂 VCEN-100 UV99.9%除菌 除病毒 杀死螨虫 拍打18,000次 (白色) 防螨</t>
+          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>使用紫外线灯可达到99.9%的除菌效果，可去除病毒。3分钟内可去除90%以上的家庭灰尘。
-从人体工学的角度设计了手柄的长度、粗细和位置，提高了握持性能。此外，通过调整重量平衡和降低主体高度以降低重心，实现了轻巧的操作性。这是雷科普史上最轻、最紧凑的“轻量化”设计。
-吸引范围扩大至165毫米，与LITE相比约扩大了20%。一次能吸尘的范围更广，短时间内高效清洁床上用品。
-新开发的“鳍打冲洗刷”在减少对床单织物的损伤的同时，还能牢牢抓住难以去除的头发和宠物的毛发。采用具有优异弹性和耐磨性的橡胶材料，每分钟敲打次数提高到18,000次。
-搭载了在空气净化器和洁净室中也使用的「HEPA(高效微粒空气) 过滤器」。保持排气的清洁，能够99.9%收集0.3微米的颗粒。* 采用全球通用100-120V插座。</t>
+          <t>在家中就能轻松应对室内灰尘的被褥吸尘器
+本体尺寸:宽30×深35.2×高15.1厘米，本体重量:1.95千克，集尘容量:0.3升
+强劲敲打:每分钟3,300次
+紫外线(UV-C)灯:6W(253.7nm)，UV杀菌:99.9%※(公益财团法人)日本食品分析中心调查 第15009593001-01号
+除尘效率: 3分钟内达到90%※由ITEA(株)东京环境过敏研究所测定 14M-RPTJUL016</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/316163kM7LL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/410AZDpyKrL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0C4KPD9VD</t>
+          <t>B09ST2ZZ4N</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
@@ -16395,13 +16139,13 @@
         </is>
       </c>
       <c r="O36" s="13">
-        <v>77371</v>
+        <v>72192</v>
       </c>
       <c r="P36" s="13">
-        <v>-78324</v>
+        <v>143748</v>
       </c>
       <c r="Q36" s="14">
-        <v>-0.75</v>
+        <v>0.66</v>
       </c>
       <c r="R36" s="15" t="inlineStr">
         <is>
@@ -16410,17 +16154,17 @@
       </c>
       <c r="S36" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T36" s="13">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="U36" s="14">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="V36" s="13">
-        <v>111436</v>
+        <v>95025</v>
       </c>
       <c r="W36" s="13"/>
       <c r="X36" s="13"/>
@@ -16428,37 +16172,37 @@
         <v>1</v>
       </c>
       <c r="Z36" s="13">
-        <v>8572</v>
+        <v>4525</v>
       </c>
       <c r="AA36" s="2"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="13"/>
       <c r="AD36" s="17">
-        <v>45</v>
+        <v>326</v>
       </c>
       <c r="AE36" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG36" s="19">
-        <v>0.15380000000000002</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="13">
         <v>532</v>
       </c>
       <c r="AI36" s="14">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="11" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="AL36" s="17">
-        <v>1643</v>
+        <v>2040</v>
       </c>
       <c r="AM36" s="11" t="inlineStr">
         <is>
@@ -16472,7 +16216,7 @@
         <v>10</v>
       </c>
       <c r="AR36" s="17">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AS36" s="12" t="inlineStr">
         <is>
@@ -16515,44 +16259,40 @@
         </is>
       </c>
       <c r="BE36" s="11"/>
-      <c r="BF36" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF36" s="11"/>
       <c r="BG36" s="11"/>
       <c r="BH36" s="12"/>
       <c r="BI36" s="20"/>
       <c r="BJ36" s="20" t="inlineStr">
         <is>
-          <t>1.9 千克</t>
+          <t>1.95 千克</t>
         </is>
       </c>
       <c r="BK36" s="20"/>
       <c r="BL36" s="20" t="inlineStr">
         <is>
-          <t>37.1長さ x 29幅 x 14.9高さ cm</t>
+          <t>35.2長さ x 30幅 x 15.1高さ cm</t>
         </is>
       </c>
       <c r="BM36" s="20"/>
       <c r="BN36" s="20" t="inlineStr">
         <is>
-          <t>3.52 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BO36" s="20" t="inlineStr">
         <is>
-          <t>3.52 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BP36" s="20" t="inlineStr">
         <is>
-          <t>41 x 31 x 19.5 cm</t>
+          <t>38.9 x 34.2 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ36" s="20" t="inlineStr">
         <is>
-          <t>41.00 x 31.00 x 19.50 cm</t>
+          <t>38.90 x 34.20 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR36" s="11" t="inlineStr">
@@ -16568,477 +16308,31 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B08XM26HKK</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>样式: 1)被褥吸尘器</t>
-        </is>
-      </c>
+          <t>B0DR1YK9LS</t>
+        </is>
+      </c>
+      <c r="D37" s="12"/>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>品牌: Raycop | 特殊功能: 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 被子 | 电源: 有线电动</t>
+          <t>品牌: エコジー | 特殊功能: HEPA, UV 灯, high_power, 无线, 无绳, 海帕, 紧凑型, 紫外线, 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 家具装饰品 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP(レイコップ)</t>
+          <t>エコジー</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
+          <t>床垫清洁器 床垫吸尘器 无线 1.2kg超轻量 UV杀菌 18Kpa 强力拍打 紧凑 病毒去除 螨虫驱除 床垫 清洁 地毯 床 花粉 螨虫防护 梅雨季节防护 螨虫清洁吸尘器 エコジー</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>在家中就能轻松应对室内灰尘的被褥吸尘器
-本体尺寸:宽30×深35.2×高15.1厘米，本体重量:1.95千克，集尘容量:0.3升
-强劲敲打:每分钟3,300次
-紫外线(UV-C)灯:6W(253.7nm)，UV杀菌:99.9%※(公益财团法人)日本食品分析中心调查 第15009593001-01号
-除尘效率: 3分钟内达到90%※由ITEA(株)东京环境过敏研究所测定 14M-RPTJUL016</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/410AZDpyKrL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>B09ST2ZZ4N</t>
-        </is>
-      </c>
-      <c r="M37" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N37" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O37" s="13">
-        <v>72192</v>
-      </c>
-      <c r="P37" s="13">
-        <v>143748</v>
-      </c>
-      <c r="Q37" s="14">
-        <v>0.66</v>
-      </c>
-      <c r="R37" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S37" s="16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="T37" s="13">
-        <v>21</v>
-      </c>
-      <c r="U37" s="14">
-        <v>1</v>
-      </c>
-      <c r="V37" s="13">
-        <v>95025</v>
-      </c>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="13">
-        <v>4525</v>
-      </c>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="17">
-        <v>326</v>
-      </c>
-      <c r="AE37" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="13">
-        <v>532</v>
-      </c>
-      <c r="AI37" s="14">
-        <v>0.81</v>
-      </c>
-      <c r="AJ37"/>
-      <c r="AK37" s="11" t="inlineStr">
-        <is>
-          <t>2021-02-26</t>
-        </is>
-      </c>
-      <c r="AL37" s="17">
-        <v>2040</v>
-      </c>
-      <c r="AM37" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN37" s="11"/>
-      <c r="AO37" s="11"/>
-      <c r="AP37" s="13"/>
-      <c r="AQ37" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR37" s="17">
-        <v>15</v>
-      </c>
-      <c r="AS37" s="12" t="inlineStr">
-        <is>
-          <t>モリハウス</t>
-        </is>
-      </c>
-      <c r="AT37" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV37" s="12" t="inlineStr">
-        <is>
-          <t>守口市竹町 大阪府 5700086 JP</t>
-        </is>
-      </c>
-      <c r="AW37" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
-        </is>
-      </c>
-      <c r="AX37" s="11"/>
-      <c r="AY37" s="11"/>
-      <c r="AZ37" s="11"/>
-      <c r="BA37" s="11"/>
-      <c r="BB37" s="11"/>
-      <c r="BC37" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD37" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE37" s="11"/>
-      <c r="BF37" s="11"/>
-      <c r="BG37" s="11"/>
-      <c r="BH37" s="12"/>
-      <c r="BI37" s="20"/>
-      <c r="BJ37" s="20" t="inlineStr">
-        <is>
-          <t>1.95 千克</t>
-        </is>
-      </c>
-      <c r="BK37" s="20"/>
-      <c r="BL37" s="20" t="inlineStr">
-        <is>
-          <t>35.2長さ x 30幅 x 15.1高さ cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="20"/>
-      <c r="BN37" s="20" t="inlineStr">
-        <is>
-          <t>2.97 kg</t>
-        </is>
-      </c>
-      <c r="BO37" s="20" t="inlineStr">
-        <is>
-          <t>2.97 kg</t>
-        </is>
-      </c>
-      <c r="BP37" s="20" t="inlineStr">
-        <is>
-          <t>38.9 x 34.2 x 19.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ37" s="20" t="inlineStr">
-        <is>
-          <t>38.90 x 34.20 x 19.20 cm</t>
-        </is>
-      </c>
-      <c r="BR37" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>B0DY61ZS3S</t>
-        </is>
-      </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Dyson | 推荐表面: 被子、床垫、沙发、靠垫、织物 | 商品重量: 60 克 | 产品的推荐用途: 被子、床垫、沙发、靠垫、精致面料 | 颜色: 银红色</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Dyson</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0DY61ZS3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>戴森 原装 戴森 Fton 工具2 500 [平行进口商品]</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>对应型号:V7/V8/V10/V11/Digital slim/V12/V15 主体尺寸(宽×深高):120.5×190×44.5mm 主体重量:0.06kg</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31dizVJn3lL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="inlineStr">
-        <is>
-          <t>B0DY61ZS3S</t>
-        </is>
-      </c>
-      <c r="M38" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N38" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O38" s="13">
-        <v>126050</v>
-      </c>
-      <c r="P38" s="13">
-        <v>191945</v>
-      </c>
-      <c r="Q38" s="14">
-        <v>0.68</v>
-      </c>
-      <c r="R38" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S38" s="16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="T38" s="13">
-        <v>16</v>
-      </c>
-      <c r="U38" s="14"/>
-      <c r="V38" s="13">
-        <v>79680</v>
-      </c>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="13">
-        <v>4980</v>
-      </c>
-      <c r="AA38" s="2"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="18">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="13">
-        <v>425</v>
-      </c>
-      <c r="AI38" s="14">
-        <v>0.76</v>
-      </c>
-      <c r="AJ38"/>
-      <c r="AK38" s="11" t="inlineStr">
-        <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AL38" s="17">
-        <v>582</v>
-      </c>
-      <c r="AM38" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN38" s="11"/>
-      <c r="AO38" s="11"/>
-      <c r="AP38" s="13"/>
-      <c r="AQ38" s="17">
-        <v>3</v>
-      </c>
-      <c r="AR38" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS38" s="12" t="inlineStr">
-        <is>
-          <t>OMITSU</t>
-        </is>
-      </c>
-      <c r="AT38" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU38" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV38" s="12" t="inlineStr">
-        <is>
-          <t>藤岡 群馬県 3750024 JP</t>
-        </is>
-      </c>
-      <c r="AW38" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZTSKKP4W4CQ6</t>
-        </is>
-      </c>
-      <c r="AX38" s="11"/>
-      <c r="AY38" s="11"/>
-      <c r="AZ38" s="11"/>
-      <c r="BA38" s="11"/>
-      <c r="BB38" s="11"/>
-      <c r="BC38" s="11"/>
-      <c r="BD38" s="11"/>
-      <c r="BE38" s="11"/>
-      <c r="BF38" s="11"/>
-      <c r="BG38" s="11"/>
-      <c r="BH38" s="12"/>
-      <c r="BI38" s="20"/>
-      <c r="BJ38" s="20" t="inlineStr">
-        <is>
-          <t>60 克</t>
-        </is>
-      </c>
-      <c r="BK38" s="20"/>
-      <c r="BL38" s="20" t="inlineStr">
-        <is>
-          <t>19長さ x 12幅 x 4.5高さ cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="20"/>
-      <c r="BN38" s="20" t="inlineStr">
-        <is>
-          <t>160 g</t>
-        </is>
-      </c>
-      <c r="BO38" s="20" t="inlineStr">
-        <is>
-          <t>160.00 g</t>
-        </is>
-      </c>
-      <c r="BP38" s="20" t="inlineStr">
-        <is>
-          <t>21.9 x 17.8 x 5.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="20" t="inlineStr">
-        <is>
-          <t>21.90 x 17.80 x 5.70 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>B0DR1YK9LS</t>
-        </is>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>品牌: エコジー | 特殊功能: HEPA, UV 灯, high_power, 无线, 无绳, 海帕, 紧凑型, 紫外线, 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 家具装饰品 | 电源: 电池供电</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>エコジー</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>床垫清洁器 床垫吸尘器 无线 1.2kg超轻量 UV杀菌 18Kpa 强力拍打 紧凑 病毒去除 螨虫驱除 床垫 清洁 地毯 床 花粉 螨虫防护 梅雨季节防护 螨虫清洁吸尘器 エコジー</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>【业界最轻量&amp;紧凑设计】本体仅重1.29千克的轻量设计。 与有线型(2.6kg)相比,使用方便,具备强大的吸力,同时即使是女性和老年人也能长时间单手使用也不会感到累。 ● 【紧凑设计】 エコジー无绳床垫清洁器尺寸为250×298×200毫米，体积小巧，节省空间。 在车内或狭窄的地方也可轻松使用,收纳方便。 【节省电费! 】1天1小时最强模式连续运转，电费仅需3日元!
 【无绳设计，舒适&amp;清洁】エコジー被褥清洁器采用无绳设计，可以在家中任何地方自由移动进行清洁。 无需担心电线会卡在家具或床上，操作起来非常顺畅。 此外，电线不会弄脏被褥或地板，在卫生方面也无需担心。 不必担心插座的位置,卧室、儿童房、车内等任何场所都可以轻松使用。
@@ -17050,19 +16344,475 @@
 【关于HEPA过滤网】请搜索HS-VC306A被褥清洁专用滤网,购买。</t>
         </is>
       </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>B0FM2MJ4B9</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O37" s="13">
+        <v>186525</v>
+      </c>
+      <c r="P37" s="13">
+        <v>1292</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>0.01</v>
+      </c>
+      <c r="R37" s="15" t="inlineStr">
+        <is>
+          <t>被褥吸尘器</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T37" s="13">
+        <v>8</v>
+      </c>
+      <c r="U37" s="14">
+        <v>-0.6</v>
+      </c>
+      <c r="V37" s="13">
+        <v>72712</v>
+      </c>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="13">
+        <v>9089</v>
+      </c>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="17">
+        <v>100</v>
+      </c>
+      <c r="AE37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>3.7</v>
+      </c>
+      <c r="AG37" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="13">
+        <v>675</v>
+      </c>
+      <c r="AI37" s="14">
+        <v>0.78</v>
+      </c>
+      <c r="AJ37"/>
+      <c r="AK37" s="11" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AL37" s="17">
+        <v>597</v>
+      </c>
+      <c r="AM37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN37" s="11"/>
+      <c r="AO37" s="11"/>
+      <c r="AP37" s="13"/>
+      <c r="AQ37" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR37" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS37" s="12" t="inlineStr">
+        <is>
+          <t>Solesenyue</t>
+        </is>
+      </c>
+      <c r="AT37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU37" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV37" s="12" t="inlineStr">
+        <is>
+          <t>深圳市 龙岗区 广东省 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB</t>
+        </is>
+      </c>
+      <c r="AX37" s="11"/>
+      <c r="AY37" s="11"/>
+      <c r="AZ37" s="11"/>
+      <c r="BA37" s="11"/>
+      <c r="BB37" s="11"/>
+      <c r="BC37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE37" s="11"/>
+      <c r="BF37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG37" s="11"/>
+      <c r="BH37" s="12"/>
+      <c r="BI37" s="20"/>
+      <c r="BJ37" s="20" t="inlineStr">
+        <is>
+          <t>1.29 千克</t>
+        </is>
+      </c>
+      <c r="BK37" s="20"/>
+      <c r="BL37" s="20" t="inlineStr">
+        <is>
+          <t>25長さ x 29.8幅 x 20高さ cm</t>
+        </is>
+      </c>
+      <c r="BM37" s="20"/>
+      <c r="BN37" s="20" t="inlineStr">
+        <is>
+          <t>2.07 kg</t>
+        </is>
+      </c>
+      <c r="BO37" s="20" t="inlineStr">
+        <is>
+          <t>2.07 kg</t>
+        </is>
+      </c>
+      <c r="BP37" s="20" t="inlineStr">
+        <is>
+          <t>34.7 x 29.4 x 22.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="20" t="inlineStr">
+        <is>
+          <t>34.70 x 29.40 x 22.90 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>B0DQSGMXJB</t>
+        </is>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>品牌: FEVORCS | 特殊功能: 高洁净度 | 筛选类型: HEPA滤网 | 推荐表面: 床垫 | 电源: 有线电动</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>FEVORCS</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>被褥吸尘器 5M线 被褥清洁器</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>双层罩杯系带式</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>B0DQSGMXJB</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
+        </is>
+      </c>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O38" s="13">
+        <v>204538</v>
+      </c>
+      <c r="P38" s="13">
+        <v>-53436</v>
+      </c>
+      <c r="Q38" s="14">
+        <v>-0.2</v>
+      </c>
+      <c r="R38" s="15" t="inlineStr">
+        <is>
+          <t>被褥吸尘器</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="T38" s="13">
+        <v>5</v>
+      </c>
+      <c r="U38" s="14">
+        <v>-0.57</v>
+      </c>
+      <c r="V38" s="13">
+        <v>49000</v>
+      </c>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="13">
+        <v>9800</v>
+      </c>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="17">
+        <v>12</v>
+      </c>
+      <c r="AE38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>4.7</v>
+      </c>
+      <c r="AG38" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="13">
+        <v>675</v>
+      </c>
+      <c r="AI38" s="14">
+        <v>0.78</v>
+      </c>
+      <c r="AJ38"/>
+      <c r="AK38" s="11" t="inlineStr">
+        <is>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="AL38" s="17">
+        <v>625</v>
+      </c>
+      <c r="AM38" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN38" s="11"/>
+      <c r="AO38" s="11"/>
+      <c r="AP38" s="13"/>
+      <c r="AQ38" s="17">
+        <v>7</v>
+      </c>
+      <c r="AR38" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="12" t="inlineStr">
+        <is>
+          <t>Koda Electrical</t>
+        </is>
+      </c>
+      <c r="AT38" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU38" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV38" s="12" t="inlineStr">
+        <is>
+          <t>苏州市 江苏省 215128 CN</t>
+        </is>
+      </c>
+      <c r="AW38" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1</t>
+        </is>
+      </c>
+      <c r="AX38" s="11"/>
+      <c r="AY38" s="11"/>
+      <c r="AZ38" s="11"/>
+      <c r="BA38" s="11"/>
+      <c r="BB38" s="11"/>
+      <c r="BC38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD38" s="11"/>
+      <c r="BE38" s="11"/>
+      <c r="BF38" s="11"/>
+      <c r="BG38" s="11"/>
+      <c r="BH38" s="12"/>
+      <c r="BI38" s="20"/>
+      <c r="BJ38" s="20" t="inlineStr">
+        <is>
+          <t>2.81 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK38" s="20" t="inlineStr">
+        <is>
+          <t>2.81 kg</t>
+        </is>
+      </c>
+      <c r="BL38" s="20" t="inlineStr">
+        <is>
+          <t>33長さ x 26.9幅 x 20.3高さ cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="20"/>
+      <c r="BN38" s="20" t="inlineStr">
+        <is>
+          <t>2.81 kg</t>
+        </is>
+      </c>
+      <c r="BO38" s="20" t="inlineStr">
+        <is>
+          <t>2.81 kg</t>
+        </is>
+      </c>
+      <c r="BP38" s="20" t="inlineStr">
+        <is>
+          <t>37.4 x 28.7 x 25.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ38" s="20" t="inlineStr">
+        <is>
+          <t>37.40 x 28.70 x 25.10 cm</t>
+        </is>
+      </c>
+      <c r="BR38" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>B01KJ6KFJU</t>
+        </is>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>品牌: Iris Ohyama | 特殊功能: 全国适用(电源 AC100V 50/60hz) | 推荐表面: 硬地板 | 电源: AC100V 50/60Hz共通 | 电压: 100 伏特</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01KJ6KFJU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 超吸引 被褥清洁剂 搭载螨虫和聚光传感器 拍打 约6000次/分钟 香槟金 KIC-FAC</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>使用时尺寸(cm):宽约25×深约45.9×高约21.2
+电源:AC100V(50/60Hz)
+功率:400W
+收纳时尺寸(cm):宽约25×深约14.4×高约40.3 ●重量:约1.6kg(包括电源线) ●电源线长度:约4m ●振动次数:每分钟约6000次 ●集尘容量:约0.2L ●套装内容:吸尘器主体、集尘过滤器(已安装在本体上)、排气过滤器(已安装在本体上)
+主体重量(千克):1.6</t>
+        </is>
+      </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B01KJ6KFJU?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/411CjY98f4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0FM2MJ4B9</t>
+          <t>B01KJ6KFJU</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -17076,13 +16826,13 @@
         </is>
       </c>
       <c r="O39" s="13">
-        <v>186525</v>
+        <v>181097</v>
       </c>
       <c r="P39" s="13">
-        <v>1292</v>
+        <v>38530</v>
       </c>
       <c r="Q39" s="14">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
@@ -17091,17 +16841,17 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T39" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39" s="14">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="V39" s="13">
-        <v>72712</v>
+        <v>48860</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
@@ -17109,19 +16859,21 @@
         <v>1</v>
       </c>
       <c r="Z39" s="13">
-        <v>9089</v>
+        <v>11350</v>
       </c>
       <c r="AA39" s="2"/>
       <c r="AB39" s="1"/>
-      <c r="AC39" s="13"/>
+      <c r="AC39" s="13">
+        <v>10</v>
+      </c>
       <c r="AD39" s="17">
-        <v>100</v>
+        <v>735</v>
       </c>
       <c r="AE39" s="13">
         <v>0</v>
       </c>
       <c r="AF39" s="18">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
@@ -17130,16 +16882,16 @@
         <v>675</v>
       </c>
       <c r="AI39" s="14">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="11" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2016-09-05</t>
         </is>
       </c>
       <c r="AL39" s="17">
-        <v>597</v>
+        <v>3675</v>
       </c>
       <c r="AM39" s="11" t="inlineStr">
         <is>
@@ -17153,11 +16905,11 @@
         <v>10</v>
       </c>
       <c r="AR39" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS39" s="12" t="inlineStr">
         <is>
-          <t>Solesenyue</t>
+          <t>TSUGUMIオンラインショップ</t>
         </is>
       </c>
       <c r="AT39" s="11" t="inlineStr">
@@ -17167,17 +16919,17 @@
       </c>
       <c r="AU39" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV39" s="12" t="inlineStr">
         <is>
-          <t>深圳市 龙岗区 广东省 518000 CN</t>
+          <t>２－１６－１９</t>
         </is>
       </c>
       <c r="AW39" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AT7SWM3E782A9</t>
         </is>
       </c>
       <c r="AX39" s="11"/>
@@ -17190,50 +16942,42 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD39" s="11"/>
       <c r="BE39" s="11"/>
-      <c r="BF39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
       <c r="BI39" s="20"/>
       <c r="BJ39" s="20" t="inlineStr">
         <is>
-          <t>1.29 千克</t>
+          <t>1.6 千克</t>
         </is>
       </c>
       <c r="BK39" s="20"/>
       <c r="BL39" s="20" t="inlineStr">
         <is>
-          <t>25長さ x 29.8幅 x 20高さ cm</t>
+          <t>45.9長さ x 25幅 x 21.2高さ cm</t>
         </is>
       </c>
       <c r="BM39" s="20"/>
       <c r="BN39" s="20" t="inlineStr">
         <is>
-          <t>2.07 kg</t>
+          <t>2.2 kg</t>
         </is>
       </c>
       <c r="BO39" s="20" t="inlineStr">
         <is>
-          <t>2.07 kg</t>
+          <t>2.20 kg</t>
         </is>
       </c>
       <c r="BP39" s="20" t="inlineStr">
         <is>
-          <t>34.7 x 29.4 x 22.9 cm</t>
+          <t>46.4 x 28 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ39" s="20" t="inlineStr">
         <is>
-          <t>34.70 x 29.40 x 22.90 cm</t>
+          <t>46.40 x 28.00 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR39" s="11" t="inlineStr">
@@ -17249,48 +16993,52 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0DQSGMXJB</t>
+          <t>B00WMD1O1M</t>
         </is>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>品牌: FEVORCS | 特殊功能: 高洁净度 | 筛选类型: HEPA滤网 | 推荐表面: 床垫 | 电源: 有线电动</t>
+          <t>品牌: Hitachi | 特殊功能: 轻巧 | 推荐表面: 家具装饰品 | 电源: 有线电动 | 随附部件: 清洁刷</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>FEVORCS</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E6%97%A5%E7%AB%8B%EF%BC%88HITACHI%EF%BC%89/page/6C6343D5-A7B7-4E5C-99C0-C7A4FD342E1F?lp_asin=B00WMD1O1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>被褥吸尘器 5M线 被褥清洁器</t>
+          <t>日立(HITACHI) 吸尘器 被褥清洁剂 强力吸力 拍打・打磨效果 约1000次/分钟 PV-FC100 N 香槟 银 通常</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>双层罩杯系带式</t>
+          <t>尺寸:18×29.5×33.2厘米
+主体重量:2.4千克
+集尘容量:0.15L
+耗电量(最大~最小):450W~约350W
+电线长度:500cm</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B00WMD1O1M?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71aNroMd8nL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0DQSGMXJB</t>
+          <t>B00WMD1O1M</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -17304,13 +17052,13 @@
         </is>
       </c>
       <c r="O40" s="13">
-        <v>204538</v>
+        <v>100119</v>
       </c>
       <c r="P40" s="13">
-        <v>-53436</v>
+        <v>174786</v>
       </c>
       <c r="Q40" s="14">
-        <v>-0.2</v>
+        <v>0.62</v>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
@@ -17319,17 +17067,17 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T40" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40" s="14">
-        <v>-0.57</v>
+        <v>-0.67</v>
       </c>
       <c r="V40" s="13">
-        <v>49000</v>
+        <v>34800</v>
       </c>
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
@@ -17337,19 +17085,21 @@
         <v>1</v>
       </c>
       <c r="Z40" s="13">
-        <v>9800</v>
+        <v>5800</v>
       </c>
       <c r="AA40" s="2"/>
       <c r="AB40" s="1"/>
-      <c r="AC40" s="13"/>
+      <c r="AC40" s="13">
+        <v>4</v>
+      </c>
       <c r="AD40" s="17">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="AE40" s="13">
         <v>0</v>
       </c>
       <c r="AF40" s="18">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG40" s="19">
         <v>0</v>
@@ -17358,16 +17108,16 @@
         <v>675</v>
       </c>
       <c r="AI40" s="14">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="11" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="AL40" s="17">
-        <v>625</v>
+        <v>4160</v>
       </c>
       <c r="AM40" s="11" t="inlineStr">
         <is>
@@ -17378,14 +17128,14 @@
       <c r="AO40" s="11"/>
       <c r="AP40" s="13"/>
       <c r="AQ40" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR40" s="17">
         <v>1</v>
       </c>
       <c r="AS40" s="12" t="inlineStr">
         <is>
-          <t>Koda Electrical</t>
+          <t>Pandora Garage</t>
         </is>
       </c>
       <c r="AT40" s="11" t="inlineStr">
@@ -17395,17 +17145,17 @@
       </c>
       <c r="AU40" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV40" s="12" t="inlineStr">
         <is>
-          <t>苏州市 江苏省 215128 CN</t>
+          <t>高尾台２－７７</t>
         </is>
       </c>
       <c r="AW40" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9MT9YALUD8PA</t>
         </is>
       </c>
       <c r="AX40" s="11"/>
@@ -17426,38 +17176,38 @@
       <c r="BI40" s="20"/>
       <c r="BJ40" s="20" t="inlineStr">
         <is>
-          <t>2.81 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK40" s="20" t="inlineStr">
-        <is>
-          <t>2.81 kg</t>
-        </is>
-      </c>
+          <t>3.4 千克</t>
+        </is>
+      </c>
+      <c r="BK40" s="20"/>
       <c r="BL40" s="20" t="inlineStr">
         <is>
-          <t>33長さ x 26.9幅 x 20.3高さ cm</t>
-        </is>
-      </c>
-      <c r="BM40" s="20"/>
+          <t>18 x 29.5 x 33.2 cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="20" t="inlineStr">
+        <is>
+          <t>18.00 x 29.50 x 33.20 cm</t>
+        </is>
+      </c>
       <c r="BN40" s="20" t="inlineStr">
         <is>
-          <t>2.81 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BO40" s="20" t="inlineStr">
         <is>
-          <t>2.81 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BP40" s="20" t="inlineStr">
         <is>
-          <t>37.4 x 28.7 x 25.1 cm</t>
+          <t>40.4 x 33.6 x 23.2 cm</t>
         </is>
       </c>
       <c r="BQ40" s="20" t="inlineStr">
         <is>
-          <t>37.40 x 28.70 x 25.10 cm</t>
+          <t>40.40 x 33.60 x 23.20 cm</t>
         </is>
       </c>
       <c r="BR40" s="11" t="inlineStr">
@@ -17473,13 +17223,13 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B01KJ6KFJU</t>
+          <t>B00M3SGXSU</t>
         </is>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>品牌: Iris Ohyama | 特殊功能: 全国适用(电源 AC100V 50/60hz) | 推荐表面: 硬地板 | 电源: AC100V 50/60Hz共通 | 电压: 100 伏特</t>
+          <t>品牌: Iris Ohyama | 特殊功能: 儿童锁,全国适用(电源 AC100V 50/60hz) | 筛选类型: HEPA。 | 推荐表面: 地毯, 家具装饰品 | 电源: 充电式</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -17489,36 +17239,32 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01KJ6KFJU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B00M3SGXSU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 超吸引 被褥清洁剂 搭载螨虫和聚光传感器 拍打 约6000次/分钟 香槟金 KIC-FAC</t>
+          <t>IRIS/OHYAMA爱丽思 无线被褥吸尘器除螨仪 白色 IC-FDC1-WP</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>使用时尺寸(cm):宽约25×深约45.9×高约21.2
-电源:AC100V(50/60Hz)
-功率:400W
-收纳时尺寸(cm):宽约25×深约14.4×高约40.3 ●重量:约1.6kg(包括电源线) ●电源线长度:约4m ●振动次数:每分钟约6000次 ●集尘容量:约0.2L ●套装内容:吸尘器主体、集尘过滤器(已安装在本体上)、排气过滤器(已安装在本体上)
-主体重量(千克):1.6</t>
+          <t>商品尺寸（cm):</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B01KJ6KFJU?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B00M3SGXSU?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/411CjY98f4L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61-+E7j+f9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B01KJ6KFJU</t>
+          <t>B00M3SGXSU</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
@@ -17532,13 +17278,13 @@
         </is>
       </c>
       <c r="O41" s="13">
-        <v>181097</v>
+        <v>150503</v>
       </c>
       <c r="P41" s="13">
-        <v>38530</v>
+        <v>-12172</v>
       </c>
       <c r="Q41" s="14">
-        <v>0.21</v>
+        <v>-0.03</v>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
@@ -17547,17 +17293,15 @@
       </c>
       <c r="S41" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T41" s="13">
-        <v>7</v>
-      </c>
-      <c r="U41" s="14">
-        <v>0.25</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U41" s="14"/>
       <c r="V41" s="13">
-        <v>48860</v>
+        <v>28000</v>
       </c>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
@@ -17565,21 +17309,21 @@
         <v>1</v>
       </c>
       <c r="Z41" s="13">
-        <v>11350</v>
+        <v>14000</v>
       </c>
       <c r="AA41" s="2"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="13">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="AD41" s="17">
-        <v>735</v>
+        <v>544</v>
       </c>
       <c r="AE41" s="13">
         <v>0</v>
       </c>
       <c r="AF41" s="18">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AG41" s="19">
         <v>0</v>
@@ -17588,16 +17332,16 @@
         <v>675</v>
       </c>
       <c r="AI41" s="14">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="11" t="inlineStr">
         <is>
-          <t>2016-09-05</t>
+          <t>2014-07-28</t>
         </is>
       </c>
       <c r="AL41" s="17">
-        <v>3675</v>
+        <v>4445</v>
       </c>
       <c r="AM41" s="11" t="inlineStr">
         <is>
@@ -17608,14 +17352,14 @@
       <c r="AO41" s="11"/>
       <c r="AP41" s="13"/>
       <c r="AQ41" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR41" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS41" s="12" t="inlineStr">
         <is>
-          <t>TSUGUMIオンラインショップ</t>
+          <t>junjun-store</t>
         </is>
       </c>
       <c r="AT41" s="11" t="inlineStr">
@@ -17630,12 +17374,12 @@
       </c>
       <c r="AV41" s="12" t="inlineStr">
         <is>
-          <t>２－１６－１９</t>
+          <t>京都市左京区 京都府 6060915 JP</t>
         </is>
       </c>
       <c r="AW41" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AT7SWM3E782A9</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CV368KAIBPF9</t>
         </is>
       </c>
       <c r="AX41" s="11"/>
@@ -17648,7 +17392,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="11"/>
+      <c r="BD41" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE41" s="11"/>
       <c r="BF41" s="11"/>
       <c r="BG41" s="11"/>
@@ -17656,34 +17404,38 @@
       <c r="BI41" s="20"/>
       <c r="BJ41" s="20" t="inlineStr">
         <is>
-          <t>1.6 千克</t>
+          <t>3000 克</t>
         </is>
       </c>
       <c r="BK41" s="20"/>
       <c r="BL41" s="20" t="inlineStr">
         <is>
-          <t>45.9長さ x 25幅 x 21.2高さ cm</t>
-        </is>
-      </c>
-      <c r="BM41" s="20"/>
+          <t>44.9 x 25.4 x 15.8 cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="20" t="inlineStr">
+        <is>
+          <t>44.90 x 25.40 x 15.80 cm</t>
+        </is>
+      </c>
       <c r="BN41" s="20" t="inlineStr">
         <is>
-          <t>2.2 kg</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BO41" s="20" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BP41" s="20" t="inlineStr">
         <is>
-          <t>46.4 x 28 x 18.4 cm</t>
+          <t>46 x 28 x 17.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="20" t="inlineStr">
         <is>
-          <t>46.40 x 28.00 x 18.40 cm</t>
+          <t>46.00 x 28.00 x 17.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="11" t="inlineStr">
@@ -17699,56 +17451,52 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0GC4TH1YT</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>尺寸: 1</t>
-        </is>
-      </c>
+          <t>B0G8CZQYDB</t>
+        </is>
+      </c>
+      <c r="D42" s="12"/>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>品牌: Joejoier | 电源: air_powered | 随附部件: 有 | 商品重量: 50 克 | 容量: 45 克</t>
+          <t>品牌: ノーブランド品 | 特殊功能: HEPA, 轻巧 | 筛选类型: 纸、不织布、聚丙烯 | 推荐表面: 被子 | 电源: 有线电动</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Joejoier</t>
+          <t>ノーブランド品</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Joejoier/page/9AC2957E-522D-4028-9735-0F53C515AC78?lp_asin=B0GC4TH1YT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>[Joejoier] 集尘清洁箱 多功能吸附盒 强力 小型吸尘器 迷你 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 时间短 &amp; 省力 Multi Functional Air Magic Box 只需这一台即可轻松打扫 汽车 办公室 客厅 卧室 厨房 厕所用 小型吸尘器</t>
+          <t>被褥清洁剂 大功率 防螨 宽头 拍打 约14000次/分钟 FCA-22H-C 象牙色</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>【多功能清洁】适用于厨房、浴室、客厅等家中的所有表面 可快速去除顽固油污垢和水垢的强力吸力。 特殊形状喷嘴可以捕捉到各个角落的灰尘。
-【静电吸附技术】微纤维和静电效果,切实捕捉花粉、螨虫、宠物的毛。 减少99%在空气中飞舞的微粒,保持最适合防过敏的清洁环境。
-【植物成分配方】内置来自天然植物的除菌凝胶。 不使用化学药品,即使是有婴儿或宠物的家庭也可放心使用。 淡淡的绿茶香气使空间清爽净化。
-节能设计:小巧机身可连续运行20分钟。 噪音级别:45dB以下,夜间使用也毫无疑问最适合在集合住宅使用。
-【简单保养】可水洗分体式结构。 湖蓝色半透明容器可以看到污垢的蓄积,不会错过更换时间。 无消耗品的经济环保设计。</t>
+          <t>使用时尺寸(cm):宽约30×深约50.1×高约21.8●收纳时尺寸(cm):宽约30×深约16.7×高约42
+质量(含电源线):约2.2千克;电源:AC100V(50/60Hz);耗电量:600W;集尘容量:约0.2升。
+拍数:每分钟约14000次;电源线长度:约4米。
+套装内容:吸尘器主体、一次性过滤网×25张(1张已安装在本体上)
+另售消耗品/一次性过滤器(25片装) CF-FT1/集尘过滤器(2个装):CF-FS2/排气过滤器(2个装):CF-FH3</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GC4TH1YT?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41D6P3WDsxL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0GC54B2HN</t>
+          <t>B0G8CZQYDB</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr">
@@ -17762,13 +17510,13 @@
         </is>
       </c>
       <c r="O42" s="13">
-        <v>54201</v>
+        <v>111494</v>
       </c>
       <c r="P42" s="13">
-        <v>34293</v>
+        <v>635634</v>
       </c>
       <c r="Q42" s="14">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="R42" s="15" t="inlineStr">
         <is>
@@ -17777,48 +17525,48 @@
       </c>
       <c r="S42" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T42" s="13">
-        <v>25</v>
-      </c>
-      <c r="U42" s="14">
-        <v>-0.85</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U42" s="14"/>
       <c r="V42" s="13">
-        <v>37200</v>
+        <v>14900</v>
       </c>
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
       <c r="Y42" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="13">
-        <v>1488</v>
+        <v>14900</v>
       </c>
       <c r="AA42" s="2"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="13"/>
-      <c r="AD42" s="17">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="18">
-        <v>1.9</v>
-      </c>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="13"/>
+      <c r="AF42" s="18"/>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
-      <c r="AH42" s="13"/>
+      <c r="AH42" s="13">
+        <v>781</v>
+      </c>
       <c r="AI42" s="14">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AJ42"/>
-      <c r="AK42" s="11"/>
-      <c r="AL42" s="17"/>
+      <c r="AK42" s="11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AL42" s="17">
+        <v>280</v>
+      </c>
       <c r="AM42" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -17835,7 +17583,7 @@
       </c>
       <c r="AS42" s="12" t="inlineStr">
         <is>
-          <t>Tan Peng Network Technology</t>
+          <t>JianShengTool</t>
         </is>
       </c>
       <c r="AT42" s="11" t="inlineStr">
@@ -17850,12 +17598,12 @@
       </c>
       <c r="AV42" s="12" t="inlineStr">
         <is>
-          <t>（郑东）金水东路49号</t>
+          <t>太原市 山西 030000 CN</t>
         </is>
       </c>
       <c r="AW42" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A20P7MISF2ZC29</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196</t>
         </is>
       </c>
       <c r="AX42" s="11"/>
@@ -17872,21 +17620,45 @@
       <c r="BI42" s="20"/>
       <c r="BJ42" s="20" t="inlineStr">
         <is>
-          <t>50 克</t>
+          <t>2.2 千克</t>
         </is>
       </c>
       <c r="BK42" s="20"/>
       <c r="BL42" s="20" t="inlineStr">
         <is>
-          <t>20長さ x 20幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="20"/>
-      <c r="BN42" s="20"/>
-      <c r="BO42" s="20"/>
-      <c r="BP42" s="20"/>
-      <c r="BQ42" s="20"/>
-      <c r="BR42" s="11"/>
+          <t>50.1 x 30 x 21.8 cm</t>
+        </is>
+      </c>
+      <c r="BM42" s="20" t="inlineStr">
+        <is>
+          <t>50.10 x 30.00 x 21.80 cm</t>
+        </is>
+      </c>
+      <c r="BN42" s="20" t="inlineStr">
+        <is>
+          <t>3.45 kg</t>
+        </is>
+      </c>
+      <c r="BO42" s="20" t="inlineStr">
+        <is>
+          <t>3.45 kg</t>
+        </is>
+      </c>
+      <c r="BP42" s="20" t="inlineStr">
+        <is>
+          <t>48.3 x 36.9 x 20.7 cm</t>
+        </is>
+      </c>
+      <c r="BQ42" s="20" t="inlineStr">
+        <is>
+          <t>48.30 x 36.90 x 20.70 cm</t>
+        </is>
+      </c>
+      <c r="BR42" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
@@ -17895,52 +17667,45 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B00WMD1O1M</t>
+          <t>B0GQC53X4K</t>
         </is>
       </c>
       <c r="D43" s="12"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Hitachi | 特殊功能: 轻巧 | 推荐表面: 家具装饰品 | 电源: 有线电动 | 随附部件: 清洁刷</t>
-        </is>
-      </c>
+      <c r="E43" s="12"/>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E6%97%A5%E7%AB%8B%EF%BC%88HITACHI%EF%BC%89/page/6C6343D5-A7B7-4E5C-99C0-C7A4FD342E1F?lp_asin=B00WMD1O1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0GQC53X4K&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>日立(HITACHI) 吸尘器 被褥清洁剂 强力吸力 拍打・打磨效果 约1000次/分钟 PV-FC100 N 香槟 银 通常</t>
+          <t>被褥烘干机 被褥清洁套装 Kararie mini 轻量款 AZJSK-S10-W IC-FAC2</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>尺寸:18×29.5×33.2厘米
-主体重量:2.4千克
-集尘容量:0.15L
-耗电量(最大~最小):450W~约350W
-电线长度:500cm</t>
+          <t>使用时尺寸(cm):宽约25×深约45.9×高约21.2
+附带Amazon.co.jp限定的香薰盒。 Kararie 史上最少的高功率。 最短8分钟,蓬松保暖。</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B00WMD1O1M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GQC53X4K?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71aNroMd8nL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31pf+NPkFKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B00WMD1O1M</t>
+          <t>B0GQC53X4K</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
@@ -17954,13 +17719,11 @@
         </is>
       </c>
       <c r="O43" s="13">
-        <v>100119</v>
-      </c>
-      <c r="P43" s="13">
-        <v>174786</v>
-      </c>
+        <v>120950</v>
+      </c>
+      <c r="P43" s="13"/>
       <c r="Q43" s="14">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
@@ -17969,154 +17732,88 @@
       </c>
       <c r="S43" s="16" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="T43" s="13">
-        <v>6</v>
-      </c>
-      <c r="U43" s="14">
-        <v>-0.67</v>
-      </c>
-      <c r="V43" s="13">
-        <v>34800</v>
-      </c>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T43" s="13"/>
+      <c r="U43" s="14"/>
+      <c r="V43" s="13"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
       <c r="Y43" s="17">
         <v>1</v>
       </c>
       <c r="Z43" s="13">
-        <v>5800</v>
+        <v>130</v>
       </c>
       <c r="AA43" s="2"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="13">
-        <v>4</v>
-      </c>
-      <c r="AD43" s="17">
-        <v>262</v>
-      </c>
+      <c r="AC43" s="13"/>
+      <c r="AD43" s="17"/>
       <c r="AE43" s="13">
         <v>0</v>
       </c>
-      <c r="AF43" s="18">
-        <v>4.3</v>
-      </c>
+      <c r="AF43" s="18"/>
       <c r="AG43" s="19">
         <v>0</v>
       </c>
-      <c r="AH43" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH43" s="13"/>
       <c r="AI43" s="14">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AJ43"/>
-      <c r="AK43" s="11" t="inlineStr">
-        <is>
-          <t>2015-05-08</t>
-        </is>
-      </c>
-      <c r="AL43" s="17">
-        <v>4160</v>
-      </c>
+      <c r="AK43" s="11"/>
+      <c r="AL43" s="17"/>
       <c r="AM43" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN43" s="11"/>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AN43" s="11" t="inlineStr">
+        <is>
+          <t>9天</t>
+        </is>
+      </c>
       <c r="AO43" s="11"/>
       <c r="AP43" s="13"/>
-      <c r="AQ43" s="17">
-        <v>9</v>
-      </c>
+      <c r="AQ43" s="17"/>
       <c r="AR43" s="17">
         <v>1</v>
       </c>
       <c r="AS43" s="12" t="inlineStr">
         <is>
-          <t>Pandora Garage</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT43" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU43" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV43" s="12" t="inlineStr">
-        <is>
-          <t>高尾台２－７７</t>
-        </is>
-      </c>
-      <c r="AW43" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9MT9YALUD8PA</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU43" s="11"/>
+      <c r="AV43" s="12"/>
+      <c r="AW43" s="11"/>
       <c r="AX43" s="11"/>
       <c r="AY43" s="11"/>
       <c r="AZ43" s="11"/>
       <c r="BA43" s="11"/>
       <c r="BB43" s="11"/>
-      <c r="BC43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC43" s="11"/>
       <c r="BD43" s="11"/>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
       <c r="BH43" s="12"/>
       <c r="BI43" s="20"/>
-      <c r="BJ43" s="20" t="inlineStr">
-        <is>
-          <t>3.4 千克</t>
-        </is>
-      </c>
+      <c r="BJ43" s="20"/>
       <c r="BK43" s="20"/>
-      <c r="BL43" s="20" t="inlineStr">
-        <is>
-          <t>18 x 29.5 x 33.2 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="20" t="inlineStr">
-        <is>
-          <t>18.00 x 29.50 x 33.20 cm</t>
-        </is>
-      </c>
-      <c r="BN43" s="20" t="inlineStr">
-        <is>
-          <t>3.5 kg</t>
-        </is>
-      </c>
-      <c r="BO43" s="20" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BP43" s="20" t="inlineStr">
-        <is>
-          <t>40.4 x 33.6 x 23.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="20" t="inlineStr">
-        <is>
-          <t>40.40 x 33.60 x 23.20 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BL43" s="20"/>
+      <c r="BM43" s="20"/>
+      <c r="BN43" s="20"/>
+      <c r="BO43" s="20"/>
+      <c r="BP43" s="20"/>
+      <c r="BQ43" s="20"/>
+      <c r="BR43" s="11"/>
     </row>
     <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
@@ -18125,13 +17822,13 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B00M3SGXSU</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>品牌: Iris Ohyama | 特殊功能: 儿童锁,全国适用(电源 AC100V 50/60hz) | 筛选类型: HEPA。 | 推荐表面: 地毯, 家具装饰品 | 电源: 充电式</t>
+          <t>品牌: Iris Ohyama | 随附部件: 无 | 外型规格: 手持式 | 制造商: アイリスオーヤマ | 商品数量: 1</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -18141,32 +17838,36 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B00M3SGXSU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>IRIS/OHYAMA爱丽思 无线被褥吸尘器除螨仪 白色 IC-FDC1-WP</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>商品尺寸（cm):</t>
+          <t>充电电源:输入:AC100V、50/60Hz、输出:DC13.7V、0.5A
+额定电压:DC10.8V
+充电时间:约 4 小时 *1 由于室温和使用时间等因素,充电时间可能会变长。
+使用温度:5~35℃
+连续使用时间 *2:标准:约 17 分钟,涡轮:约 8 分钟,自动:约 8-24 分钟 *2 充满电,电池初始温度:20 ℃。</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B00M3SGXSU?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61-+E7j+f9L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B00M3SGXSU</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="M44" s="12" t="inlineStr">
@@ -18180,10 +17881,10 @@
         </is>
       </c>
       <c r="O44" s="13">
-        <v>150503</v>
+        <v>40209</v>
       </c>
       <c r="P44" s="13">
-        <v>-12172</v>
+        <v>-36073</v>
       </c>
       <c r="Q44" s="14">
         <v>-0.03</v>
@@ -18195,55 +17896,41 @@
       </c>
       <c r="S44" s="16" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="T44" s="13">
-        <v>2</v>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T44" s="13"/>
       <c r="U44" s="14"/>
-      <c r="V44" s="13">
-        <v>28000</v>
-      </c>
+      <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="13"/>
       <c r="Y44" s="17">
         <v>1</v>
       </c>
       <c r="Z44" s="13">
-        <v>14000</v>
+        <v>19478</v>
       </c>
       <c r="AA44" s="2"/>
       <c r="AB44" s="1"/>
-      <c r="AC44" s="13">
-        <v>31</v>
-      </c>
-      <c r="AD44" s="17">
-        <v>544</v>
-      </c>
-      <c r="AE44" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="18">
-        <v>3.7</v>
-      </c>
+      <c r="AC44" s="13"/>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="13"/>
+      <c r="AF44" s="18"/>
       <c r="AG44" s="19">
         <v>0</v>
       </c>
-      <c r="AH44" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH44" s="13"/>
       <c r="AI44" s="14">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="11" t="inlineStr">
         <is>
-          <t>2014-07-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AL44" s="17">
-        <v>4445</v>
+        <v>96</v>
       </c>
       <c r="AM44" s="11" t="inlineStr">
         <is>
@@ -18253,15 +17940,13 @@
       <c r="AN44" s="11"/>
       <c r="AO44" s="11"/>
       <c r="AP44" s="13"/>
-      <c r="AQ44" s="17">
-        <v>8</v>
-      </c>
+      <c r="AQ44" s="17"/>
       <c r="AR44" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS44" s="12" t="inlineStr">
         <is>
-          <t>junjun-store</t>
+          <t>ダイユーエイト【「在庫あり」表示の商品は祝日も発送しております-土日は休みです-】</t>
         </is>
       </c>
       <c r="AT44" s="11" t="inlineStr">
@@ -18276,12 +17961,12 @@
       </c>
       <c r="AV44" s="12" t="inlineStr">
         <is>
-          <t>京都市左京区 京都府 6060915 JP</t>
+          <t>福島市 福島県 9608151 JP</t>
         </is>
       </c>
       <c r="AW44" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CV368KAIBPF9</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A8LGULJOES9Z</t>
         </is>
       </c>
       <c r="AX44" s="11"/>
@@ -18289,1388 +17974,22 @@
       <c r="AZ44" s="11"/>
       <c r="BA44" s="11"/>
       <c r="BB44" s="11"/>
-      <c r="BC44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="11"/>
+      <c r="BD44" s="11"/>
       <c r="BE44" s="11"/>
       <c r="BF44" s="11"/>
       <c r="BG44" s="11"/>
       <c r="BH44" s="12"/>
       <c r="BI44" s="20"/>
-      <c r="BJ44" s="20" t="inlineStr">
-        <is>
-          <t>3000 克</t>
-        </is>
-      </c>
+      <c r="BJ44" s="20"/>
       <c r="BK44" s="20"/>
-      <c r="BL44" s="20" t="inlineStr">
-        <is>
-          <t>44.9 x 25.4 x 15.8 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="20" t="inlineStr">
-        <is>
-          <t>44.90 x 25.40 x 15.80 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="20" t="inlineStr">
-        <is>
-          <t>3 kg</t>
-        </is>
-      </c>
-      <c r="BO44" s="20" t="inlineStr">
-        <is>
-          <t>3.00 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="20" t="inlineStr">
-        <is>
-          <t>46 x 28 x 17.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ44" s="20" t="inlineStr">
-        <is>
-          <t>46.00 x 28.00 x 17.50 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B0G8CZQYDB</t>
-        </is>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>品牌: ノーブランド品 | 特殊功能: HEPA, 轻巧 | 筛选类型: 纸、不织布、聚丙烯 | 推荐表面: 被子 | 电源: 有线电动</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>ノーブランド品</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>被褥清洁剂 大功率 防螨 宽头 拍打 约14000次/分钟 FCA-22H-C 象牙色</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>使用时尺寸(cm):宽约30×深约50.1×高约21.8●收纳时尺寸(cm):宽约30×深约16.7×高约42
-质量(含电源线):约2.2千克;电源:AC100V(50/60Hz);耗电量:600W;集尘容量:约0.2升。
-拍数:每分钟约14000次;电源线长度:约4米。
-套装内容:吸尘器主体、一次性过滤网×25张(1张已安装在本体上)
-另售消耗品/一次性过滤器(25片装) CF-FT1/集尘过滤器(2个装):CF-FS2/排气过滤器(2个装):CF-FH3</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B0G8CZQYDB</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O45" s="13">
-        <v>111494</v>
-      </c>
-      <c r="P45" s="13">
-        <v>635634</v>
-      </c>
-      <c r="Q45" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="R45" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="T45" s="13">
-        <v>1</v>
-      </c>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13">
-        <v>14900</v>
-      </c>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="13">
-        <v>14900</v>
-      </c>
-      <c r="AA45" s="2"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="13"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="13"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="13">
-        <v>781</v>
-      </c>
-      <c r="AI45" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="11" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AL45" s="17">
-        <v>280</v>
-      </c>
-      <c r="AM45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45" s="13"/>
-      <c r="AQ45" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR45" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS45" s="12" t="inlineStr">
-        <is>
-          <t>JianShengTool</t>
-        </is>
-      </c>
-      <c r="AT45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU45" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV45" s="12" t="inlineStr">
-        <is>
-          <t>太原市 山西 030000 CN</t>
-        </is>
-      </c>
-      <c r="AW45" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196</t>
-        </is>
-      </c>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="20"/>
-      <c r="BJ45" s="20" t="inlineStr">
-        <is>
-          <t>2.2 千克</t>
-        </is>
-      </c>
-      <c r="BK45" s="20"/>
-      <c r="BL45" s="20" t="inlineStr">
-        <is>
-          <t>50.1 x 30 x 21.8 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="20" t="inlineStr">
-        <is>
-          <t>50.10 x 30.00 x 21.80 cm</t>
-        </is>
-      </c>
-      <c r="BN45" s="20" t="inlineStr">
-        <is>
-          <t>3.45 kg</t>
-        </is>
-      </c>
-      <c r="BO45" s="20" t="inlineStr">
-        <is>
-          <t>3.45 kg</t>
-        </is>
-      </c>
-      <c r="BP45" s="20" t="inlineStr">
-        <is>
-          <t>48.3 x 36.9 x 20.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ45" s="20" t="inlineStr">
-        <is>
-          <t>48.30 x 36.90 x 20.70 cm</t>
-        </is>
-      </c>
-      <c r="BR45" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0HJBYGLLS</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 集尘盒*2</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Yizibuur | 颜色: 集尘盒*2 | 型号名称: VSKIN21780 | 商品尺寸: 10长度 x 10宽度 x 10高度 毫米 | 制造商: Yizibuur</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Yizibuur</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Yizibuur/page/16D746F6-5F31-4921-AAB0-B9944FFD45C3?lp_asin=B0HJBYGLLS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>防尘箱【除灰尘】多功能除尘箱【房屋灰尘的救星】 汽车 办公室 客厅 卧室 厨房 厕所用</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>【多功能清洁】适用于厨房、浴室、客厅等家中的各种表面。 实现强大的吸力,可快速去除顽固的油渍和水垢。 特殊形状的喷嘴可以捕捉到各个角落的灰尘。
-[静电吸附技术] 通过超细纤维和静电效果,能够确实捕捉花粉、螨虫、宠物毛。 阻隔99%空气中飞出的微粒,保持最适合防止过敏的清洁环境。
-[含有植物成分] 内置来自天然植物的消毒凝胶。 不使用化学药品,有婴儿和宠物的家庭也可放心使用。 淡淡的绿茶香味可以清爽地净化空间。
-【节能设计】小巧机身,可连续运行20分钟。 噪音水平在45dB以下,不必担心夜间使用,非常适合集体住宅使用。
-【简单保养】可水洗的可拆卸式结构。 湖蓝色半透明容器,可看到污垢积累,不会错过更换时间。 无消耗品的经济环保设计。</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HJBYGLLS?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41D9mkEdSsL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0HJBVZYD7</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O46" s="13">
-        <v>78230</v>
-      </c>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="14">
-        <v>0</v>
-      </c>
-      <c r="R46" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S46" s="16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T46" s="13">
-        <v>2</v>
-      </c>
-      <c r="U46" s="14"/>
-      <c r="V46" s="13">
-        <v>3176</v>
-      </c>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="17">
-        <v>8</v>
-      </c>
-      <c r="Z46" s="13">
-        <v>1588</v>
-      </c>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE46" s="13"/>
-      <c r="AF46" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="13"/>
-      <c r="AI46" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AL46" s="17">
-        <v>16</v>
-      </c>
-      <c r="AM46" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46" s="13"/>
-      <c r="AQ46" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR46" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS46" s="12" t="inlineStr">
-        <is>
-          <t>XiZou e-commerce(跟卖必下单投诉）</t>
-        </is>
-      </c>
-      <c r="AT46" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU46" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV46" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW46" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2Q4HC9SZPWZ92</t>
-        </is>
-      </c>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="20"/>
-      <c r="BJ46" s="20" t="inlineStr">
-        <is>
-          <t>10 g</t>
-        </is>
-      </c>
-      <c r="BK46" s="20" t="inlineStr">
-        <is>
-          <t>10.00 g</t>
-        </is>
-      </c>
-      <c r="BL46" s="20" t="inlineStr">
-        <is>
-          <t>10長さ x 10幅 x 10高さ mm</t>
-        </is>
-      </c>
-      <c r="BM46" s="20"/>
-      <c r="BN46" s="20" t="inlineStr">
-        <is>
-          <t>10 g</t>
-        </is>
-      </c>
-      <c r="BO46" s="20" t="inlineStr">
-        <is>
-          <t>10.00 g</t>
-        </is>
-      </c>
-      <c r="BP46" s="20"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0GF6NKQZM</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 集尘盒4个</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>品牌: JUELREOU | 电源: air_powered | 随附部件: 有 | 商品重量: 50 克 | 容量: 45 克</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JUELREOU</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU【除尘】集尘清洁箱【2026最新】 强力 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 Multi Functional Air Magic Box 汽车 办公室 客厅 卧室 厨房 厕所用</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>【多功能清洁】适用于厨房、浴室、客厅等家中的所有表面 可快速去除顽固油污垢和水垢的强力吸力。 特殊形状喷嘴可以捕捉到各个角落的灰尘。
-【静电吸附技术】微纤维和静电效果,切实捕捉花粉、螨虫、宠物的毛。 减少99%在空气中飞舞的微粒,保持最适合防过敏的清洁环境。
-【植物成分配方】内置来自天然植物的除菌凝胶。 不使用化学药品,即使是有婴儿或宠物的家庭也可放心使用。 淡淡的绿茶香气使空间清爽净化。
-节能设计:小巧机身可连续运行20分钟。 噪音级别:45dB以下,夜间使用也毫无疑问最适合在集合住宅使用。
-【简单保养】可水洗分体式结构。 湖蓝色半透明容器可以看到污垢的蓄积,不会错过更换时间。 无消耗品的经济环保设计。</t>
-        </is>
-      </c>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GF6NKQZM?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51fS2kS-e7L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>B0GF6361S2</t>
-        </is>
-      </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N47" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O47" s="13">
-        <v>111779</v>
-      </c>
-      <c r="P47" s="13">
-        <v>309925</v>
-      </c>
-      <c r="Q47" s="14">
-        <v>0.73</v>
-      </c>
-      <c r="R47" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S47" s="16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T47" s="13">
-        <v>1</v>
-      </c>
-      <c r="U47" s="14">
-        <v>-1</v>
-      </c>
-      <c r="V47" s="13">
-        <v>1180</v>
-      </c>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="17">
-        <v>15</v>
-      </c>
-      <c r="Z47" s="13">
-        <v>1180</v>
-      </c>
-      <c r="AA47" s="2"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="18">
-        <v>1</v>
-      </c>
-      <c r="AG47" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
-      <c r="AL47" s="17">
-        <v>253</v>
-      </c>
-      <c r="AM47" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47" s="13"/>
-      <c r="AQ47" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR47" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU（通常、5〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="AT47" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU47" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV47" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW47" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1VJKLQTDJXYI3</t>
-        </is>
-      </c>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11"/>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="20"/>
-      <c r="BJ47" s="20" t="inlineStr">
-        <is>
-          <t>50 克</t>
-        </is>
-      </c>
-      <c r="BK47" s="20"/>
-      <c r="BL47" s="20" t="inlineStr">
-        <is>
-          <t>20長さ x 20幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="20"/>
-      <c r="BN47" s="20" t="inlineStr">
-        <is>
-          <t>100 g</t>
-        </is>
-      </c>
-      <c r="BO47" s="20" t="inlineStr">
-        <is>
-          <t>100.00 g</t>
-        </is>
-      </c>
-      <c r="BP47" s="20"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0DJ74YT3F</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>品牌: ノーブランド品 | 颜色: 白色，黑色 | 商品重量: 0.5 千克 | 商品尺寸: 14.6深度 x 24.8宽度 x 31.2高度 厘米 | 样式: 单品</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>ノーブランド品</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>LINCEER 吸尘器 小巧型 【电视放映商品】</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>电源:AC100V・50・60Hz
-额定功率:330W
-吸尘功率:30W
-回收罐有效容量:0.5L
-满水箱容量:0.3升
-在清洗沙发或地毯等布制品时非常方便。 用喷雾喷水,漂浮污垢,水一起回收。</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0DJ74YT3F?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/51HYSf+5dLL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0DJ74YT3F</t>
-        </is>
-      </c>
-      <c r="M48" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O48" s="13">
-        <v>189013</v>
-      </c>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="14">
-        <v>0</v>
-      </c>
-      <c r="R48" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T48" s="13"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="13">
-        <v>9220</v>
-      </c>
-      <c r="AA48" s="2"/>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AL48" s="17">
-        <v>730</v>
-      </c>
-      <c r="AM48" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48" s="13"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS48" s="12" t="inlineStr">
-        <is>
-          <t>gznllsmyxgs</t>
-        </is>
-      </c>
-      <c r="AT48" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU48" s="11"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EECRONKD22AZ</t>
-        </is>
-      </c>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20" t="inlineStr">
-        <is>
-          <t>0.5 千克</t>
-        </is>
-      </c>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20" t="inlineStr">
-        <is>
-          <t>14.6奥行き x 24.8幅 x 31.2高さ cm</t>
-        </is>
-      </c>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0GQC53X4K</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0GQC53X4K&amp;ref_=ast_bln</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>被褥烘干机 被褥清洁套装 Kararie mini 轻量款 AZJSK-S10-W IC-FAC2</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>使用时尺寸(cm):宽约25×深约45.9×高约21.2
-附带Amazon.co.jp限定的香薰盒。 Kararie 史上最少的高功率。 最短8分钟,蓬松保暖。</t>
-        </is>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GQC53X4K?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31pf+NPkFKL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0GQC53X4K</t>
-        </is>
-      </c>
-      <c r="M49" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N49" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O49" s="13">
-        <v>120950</v>
-      </c>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="14">
-        <v>0</v>
-      </c>
-      <c r="R49" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S49" s="16" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T49" s="13"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="13">
-        <v>130</v>
-      </c>
-      <c r="AA49" s="2"/>
-      <c r="AB49" s="1"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN49" s="11" t="inlineStr">
-        <is>
-          <t>9天</t>
-        </is>
-      </c>
-      <c r="AO49" s="11"/>
-      <c r="AP49" s="13"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT49" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU49" s="11"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Iris Ohyama | 随附部件: 无 | 外型规格: 手持式 | 制造商: アイリスオーヤマ | 商品数量: 1</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>充电电源:输入:AC100V、50/60Hz、输出:DC13.7V、0.5A
-额定电压:DC10.8V
-充电时间:约 4 小时 *1 由于室温和使用时间等因素,充电时间可能会变长。
-使用温度:5~35℃
-连续使用时间 *2:标准:约 17 分钟,涡轮:约 8 分钟,自动:约 8-24 分钟 *2 充满电,电池初始温度:20 ℃。</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N50" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O50" s="13">
-        <v>40209</v>
-      </c>
-      <c r="P50" s="13">
-        <v>-36073</v>
-      </c>
-      <c r="Q50" s="14">
-        <v>-0.03</v>
-      </c>
-      <c r="R50" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="13">
-        <v>19478</v>
-      </c>
-      <c r="AA50" s="2"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="17"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AL50" s="17">
-        <v>96</v>
-      </c>
-      <c r="AM50" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50" s="13"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50" s="17">
-        <v>3</v>
-      </c>
-      <c r="AS50" s="12" t="inlineStr">
-        <is>
-          <t>ダイユーエイト【「在庫あり」表示の商品は祝日も発送しております-土日は休みです-】</t>
-        </is>
-      </c>
-      <c r="AT50" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU50" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV50" s="12" t="inlineStr">
-        <is>
-          <t>福島市 福島県 9608151 JP</t>
-        </is>
-      </c>
-      <c r="AW50" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A8LGULJOES9Z</t>
-        </is>
-      </c>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50" s="20"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0H6FQR9YH</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>商品数量: 1</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>品牌: pronala | 颜色: 新版本1个 | 商品尺寸: 10长度 x 10宽度 x 10高度 毫米 | 制造商: 1 | 商品数量: 1</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>pronala</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=pronala</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>尘箱【除霉真神】超强吸霉全天候清洁净化器【除尘】强力 多功能 24小时自动吸附灰尘 大容量 省时打扫健康呼吸空间 家庭 客厅 卧室 厨房 托儿所 宠物区适用 (1)</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>1.【除尘清洁箱 防霉菌・灰尘净化器】多功能清洁装置,可同时抑制霉菌和集尘,强力吸附性能能够牢牢捕捉室内漂浮灰尘,全年全天候保持室内空气清洁。
-2.24 小时自动工作设计,无需费时集尘。 大幅缩短清扫的麻烦,抑制飞舞的细小粉尘和霉菌孢子,保持干净易呼吸的室内环境。
-3.大容量收纳结构,无需频繁丢弃垃圾,除尘处理能力优异,即使长时间连续使用也不易降低吸附力,减轻每天的家务负担。
-4.除了客厅、卧室、厨房等普通家庭外,也非常适合宠物饲养空间和托儿所。 解决宠物脱发、食物残渣和室内霉菌的问题。
-5.不挑放置场所的小巧机身,设置简单。 应对家中的灰尘、霉菌问题,保护家庭健康的空间清洁必备品。</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6FQR9YH?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41fVQlgC0NL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0H6FFPG8Y</t>
-        </is>
-      </c>
-      <c r="M51" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O51" s="13">
-        <v>116681</v>
-      </c>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14">
-        <v>0</v>
-      </c>
-      <c r="R51" s="15" t="inlineStr">
-        <is>
-          <t>被褥吸尘器</t>
-        </is>
-      </c>
-      <c r="S51" s="16" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17">
-        <v>6</v>
-      </c>
-      <c r="Z51" s="13">
-        <v>1488</v>
-      </c>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51" s="13"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="12" t="inlineStr">
-        <is>
-          <t>配送3～11日以内PronalaShop-JP</t>
-        </is>
-      </c>
-      <c r="AT51" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV51" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW51" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TBQ5YA5MO311</t>
-        </is>
-      </c>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20" t="inlineStr">
-        <is>
-          <t>10長さ x 10幅 x 10高さ mm</t>
-        </is>
-      </c>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
+      <c r="BL44" s="20"/>
+      <c r="BM44" s="20"/>
+      <c r="BN44" s="20"/>
+      <c r="BO44" s="20"/>
+      <c r="BP44" s="20"/>
+      <c r="BQ44" s="20"/>
+      <c r="BR44" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19935,149 +18254,93 @@
     <hyperlink ref="M34" r:id="rId257" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N34" r:id="rId258"/>
     <hyperlink ref="AW34" r:id="rId259" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A6GQC2WH356ZN"/>
-    <hyperlink ref="C35" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0CLKZM25S"/>
-    <hyperlink ref="G35" r:id="rId261" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0CLKZM25S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J35" r:id="rId262" tooltip="https://www.amazon.co.jp/dp/B0CLKZM25S?psc=1"/>
-    <hyperlink ref="K35" r:id="rId263" tooltip="https://m.media-amazon.com/images/I/41OndC98uCL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0CLKZM25S"/>
+    <hyperlink ref="C35" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
+    <hyperlink ref="G35" r:id="rId261" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09WMDJ3R8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId262" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1"/>
+    <hyperlink ref="K35" r:id="rId263" tooltip="https://m.media-amazon.com/images/I/316163kM7LL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0C4KPD9VD"/>
     <hyperlink ref="M35" r:id="rId265" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N35" r:id="rId266"/>
-    <hyperlink ref="AW35" r:id="rId267" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A96F6A3HJYHX0"/>
-    <hyperlink ref="C36" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8"/>
-    <hyperlink ref="G36" r:id="rId269" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09WMDJ3R8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId270" tooltip="https://www.amazon.co.jp/dp/B09WMDJ3R8?psc=1"/>
-    <hyperlink ref="K36" r:id="rId271" tooltip="https://m.media-amazon.com/images/I/316163kM7LL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B0C4KPD9VD"/>
+    <hyperlink ref="AW35" r:id="rId267" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
+    <hyperlink ref="C36" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
+    <hyperlink ref="G36" r:id="rId269" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId270" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
+    <hyperlink ref="K36" r:id="rId271" tooltip="https://m.media-amazon.com/images/I/410AZDpyKrL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B09ST2ZZ4N"/>
     <hyperlink ref="M36" r:id="rId273" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N36" r:id="rId274"/>
     <hyperlink ref="AW36" r:id="rId275" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
-    <hyperlink ref="C37" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
-    <hyperlink ref="G37" r:id="rId277" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
-    <hyperlink ref="K37" r:id="rId279" tooltip="https://m.media-amazon.com/images/I/410AZDpyKrL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B09ST2ZZ4N"/>
+    <hyperlink ref="C37" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
+    <hyperlink ref="G37" r:id="rId277" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln"/>
+    <hyperlink ref="J37" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
+    <hyperlink ref="K37" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B0FM2MJ4B9"/>
     <hyperlink ref="M37" r:id="rId281" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N37" r:id="rId282"/>
-    <hyperlink ref="AW37" r:id="rId283" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
-    <hyperlink ref="C38" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
-    <hyperlink ref="G38" r:id="rId285" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0DY61ZS3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1"/>
-    <hyperlink ref="K38" r:id="rId287" tooltip="https://m.media-amazon.com/images/I/31dizVJn3lL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
+    <hyperlink ref="AW37" r:id="rId283" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB"/>
+    <hyperlink ref="C38" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
+    <hyperlink ref="G38" r:id="rId285" tooltip="https://www.amazon.co.jp/-/zh/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1"/>
+    <hyperlink ref="K38" r:id="rId287" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
     <hyperlink ref="M38" r:id="rId289" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N38" r:id="rId290"/>
-    <hyperlink ref="AW38" r:id="rId291" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZTSKKP4W4CQ6"/>
-    <hyperlink ref="C39" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
-    <hyperlink ref="G39" r:id="rId293" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln"/>
-    <hyperlink ref="J39" r:id="rId294" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
-    <hyperlink ref="K39" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0FM2MJ4B9"/>
+    <hyperlink ref="AW38" r:id="rId291" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1"/>
+    <hyperlink ref="C39" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU"/>
+    <hyperlink ref="G39" r:id="rId293" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01KJ6KFJU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId294" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU?psc=1"/>
+    <hyperlink ref="K39" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/411CjY98f4L._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU"/>
     <hyperlink ref="M39" r:id="rId297" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N39" r:id="rId298"/>
-    <hyperlink ref="AW39" r:id="rId299" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB"/>
-    <hyperlink ref="C40" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
-    <hyperlink ref="G40" r:id="rId301" tooltip="https://www.amazon.co.jp/-/zh/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1"/>
-    <hyperlink ref="K40" r:id="rId303" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
+    <hyperlink ref="AW39" r:id="rId299" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AT7SWM3E782A9"/>
+    <hyperlink ref="C40" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M"/>
+    <hyperlink ref="G40" r:id="rId301" tooltip="https://www.amazon.co.jp/stores/%E6%97%A5%E7%AB%8B%EF%BC%88HITACHI%EF%BC%89/page/6C6343D5-A7B7-4E5C-99C0-C7A4FD342E1F?lp_asin=B00WMD1O1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M?psc=1"/>
+    <hyperlink ref="K40" r:id="rId303" tooltip="https://images-na.ssl-images-amazon.com/images/I/71aNroMd8nL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M"/>
     <hyperlink ref="M40" r:id="rId305" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N40" r:id="rId306"/>
-    <hyperlink ref="AW40" r:id="rId307" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1"/>
-    <hyperlink ref="C41" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU"/>
-    <hyperlink ref="G41" r:id="rId309" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01KJ6KFJU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU?psc=1"/>
-    <hyperlink ref="K41" r:id="rId311" tooltip="https://images-na.ssl-images-amazon.com/images/I/411CjY98f4L._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B01KJ6KFJU"/>
+    <hyperlink ref="AW40" r:id="rId307" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9MT9YALUD8PA"/>
+    <hyperlink ref="C41" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU"/>
+    <hyperlink ref="G41" r:id="rId309" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B00M3SGXSU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU?psc=1"/>
+    <hyperlink ref="K41" r:id="rId311" tooltip="https://images-na.ssl-images-amazon.com/images/I/61-+E7j+f9L._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU"/>
     <hyperlink ref="M41" r:id="rId313" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N41" r:id="rId314"/>
-    <hyperlink ref="AW41" r:id="rId315" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AT7SWM3E782A9"/>
-    <hyperlink ref="C42" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0GC4TH1YT"/>
-    <hyperlink ref="G42" r:id="rId317" tooltip="https://www.amazon.co.jp/-/zh/stores/Joejoier/page/9AC2957E-522D-4028-9735-0F53C515AC78?lp_asin=B0GC4TH1YT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0GC4TH1YT?psc=1"/>
-    <hyperlink ref="K42" r:id="rId319" tooltip="https://m.media-amazon.com/images/I/41D6P3WDsxL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0GC54B2HN"/>
+    <hyperlink ref="AW41" r:id="rId315" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CV368KAIBPF9"/>
+    <hyperlink ref="C42" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
+    <hyperlink ref="G42" r:id="rId317" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81"/>
+    <hyperlink ref="J42" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1"/>
+    <hyperlink ref="K42" r:id="rId319" tooltip="https://images-na.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
     <hyperlink ref="M42" r:id="rId321" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N42" r:id="rId322"/>
-    <hyperlink ref="AW42" r:id="rId323" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A20P7MISF2ZC29"/>
-    <hyperlink ref="C43" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M"/>
-    <hyperlink ref="G43" r:id="rId325" tooltip="https://www.amazon.co.jp/stores/%E6%97%A5%E7%AB%8B%EF%BC%88HITACHI%EF%BC%89/page/6C6343D5-A7B7-4E5C-99C0-C7A4FD342E1F?lp_asin=B00WMD1O1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M?psc=1"/>
-    <hyperlink ref="K43" r:id="rId327" tooltip="https://images-na.ssl-images-amazon.com/images/I/71aNroMd8nL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B00WMD1O1M"/>
+    <hyperlink ref="AW42" r:id="rId323" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196"/>
+    <hyperlink ref="C43" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K"/>
+    <hyperlink ref="G43" r:id="rId325" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0GQC53X4K&amp;ref_=ast_bln"/>
+    <hyperlink ref="J43" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K?psc=1"/>
+    <hyperlink ref="K43" r:id="rId327" tooltip="https://m.media-amazon.com/images/I/31pf+NPkFKL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K"/>
     <hyperlink ref="M43" r:id="rId329" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N43" r:id="rId330"/>
-    <hyperlink ref="AW43" r:id="rId331" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9MT9YALUD8PA"/>
-    <hyperlink ref="C44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU"/>
-    <hyperlink ref="G44" r:id="rId333" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B00M3SGXSU&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU?psc=1"/>
-    <hyperlink ref="K44" r:id="rId335" tooltip="https://images-na.ssl-images-amazon.com/images/I/61-+E7j+f9L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B00M3SGXSU"/>
-    <hyperlink ref="M44" r:id="rId337" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N44" r:id="rId338"/>
-    <hyperlink ref="AW44" r:id="rId339" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CV368KAIBPF9"/>
-    <hyperlink ref="C45" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
-    <hyperlink ref="G45" r:id="rId341" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81"/>
-    <hyperlink ref="J45" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB?psc=1"/>
-    <hyperlink ref="K45" r:id="rId343" tooltip="https://images-na.ssl-images-amazon.com/images/I/41n3vCS-qhL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0G8CZQYDB"/>
-    <hyperlink ref="M45" r:id="rId345" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N45" r:id="rId346"/>
-    <hyperlink ref="AW45" r:id="rId347" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196"/>
-    <hyperlink ref="C46" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0HJBYGLLS"/>
-    <hyperlink ref="G46" r:id="rId349" tooltip="https://www.amazon.co.jp/-/zh/stores/Yizibuur/page/16D746F6-5F31-4921-AAB0-B9944FFD45C3?lp_asin=B0HJBYGLLS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0HJBYGLLS?psc=1"/>
-    <hyperlink ref="K46" r:id="rId351" tooltip="https://m.media-amazon.com/images/I/41D9mkEdSsL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0HJBVZYD7"/>
-    <hyperlink ref="M46" r:id="rId353" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N46" r:id="rId354"/>
-    <hyperlink ref="AW46" r:id="rId355" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2Q4HC9SZPWZ92"/>
-    <hyperlink ref="C47" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0GF6NKQZM"/>
-    <hyperlink ref="G47" r:id="rId357" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JUELREOU"/>
-    <hyperlink ref="J47" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0GF6NKQZM?psc=1"/>
-    <hyperlink ref="K47" r:id="rId359" tooltip="https://m.media-amazon.com/images/I/51fS2kS-e7L._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId360" tooltip="https://www.amazon.co.jp/dp/B0GF6361S2"/>
-    <hyperlink ref="M47" r:id="rId361" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N47" r:id="rId362"/>
-    <hyperlink ref="AW47" r:id="rId363" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1VJKLQTDJXYI3"/>
-    <hyperlink ref="C48" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B0DJ74YT3F"/>
-    <hyperlink ref="G48" r:id="rId365" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81"/>
-    <hyperlink ref="J48" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B0DJ74YT3F?psc=1"/>
-    <hyperlink ref="K48" r:id="rId367" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/51HYSf+5dLL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId368" tooltip="https://www.amazon.co.jp/dp/B0DJ74YT3F"/>
-    <hyperlink ref="M48" r:id="rId369" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N48" r:id="rId370"/>
-    <hyperlink ref="AW48" r:id="rId371" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EECRONKD22AZ"/>
-    <hyperlink ref="C49" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K"/>
-    <hyperlink ref="G49" r:id="rId373" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0GQC53X4K&amp;ref_=ast_bln"/>
-    <hyperlink ref="J49" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K?psc=1"/>
-    <hyperlink ref="K49" r:id="rId375" tooltip="https://m.media-amazon.com/images/I/31pf+NPkFKL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId376" tooltip="https://www.amazon.co.jp/dp/B0GQC53X4K"/>
-    <hyperlink ref="M49" r:id="rId377" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N49" r:id="rId378"/>
-    <hyperlink ref="C50" r:id="rId379" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="G50" r:id="rId380" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId381" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
-    <hyperlink ref="K50" r:id="rId382" tooltip="https://images-na.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId383" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="M50" r:id="rId384" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N50" r:id="rId385"/>
-    <hyperlink ref="AW50" r:id="rId386" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A8LGULJOES9Z"/>
-    <hyperlink ref="C51" r:id="rId387" tooltip="https://www.amazon.co.jp/dp/B0H6FQR9YH"/>
-    <hyperlink ref="G51" r:id="rId388" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=pronala"/>
-    <hyperlink ref="J51" r:id="rId389" tooltip="https://www.amazon.co.jp/dp/B0H6FQR9YH?psc=1"/>
-    <hyperlink ref="K51" r:id="rId390" tooltip="https://m.media-amazon.com/images/I/41fVQlgC0NL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId391" tooltip="https://www.amazon.co.jp/dp/B0H6FFPG8Y"/>
-    <hyperlink ref="M51" r:id="rId392" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N51" r:id="rId393"/>
-    <hyperlink ref="AW51" r:id="rId394" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TBQ5YA5MO311"/>
+    <hyperlink ref="C44" r:id="rId331" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
+    <hyperlink ref="G44" r:id="rId332" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId333" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
+    <hyperlink ref="K44" r:id="rId334" tooltip="https://images-na.ssl-images-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId335" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
+    <hyperlink ref="M44" r:id="rId336" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
+    <hyperlink ref="N44" r:id="rId337"/>
+    <hyperlink ref="AW44" r:id="rId338" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A8LGULJOES9Z"/>
   </hyperlinks>
-  <drawing r:id="rId395"/>
+  <drawing r:id="rId339"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -20141,7 +18404,7 @@
         <v>31341.739210850803</v>
       </c>
       <c r="G2" s="19">
-        <v>0.20224438902743141</v>
+        <v>0.203436598520005</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20162,7 +18425,7 @@
         <v>13183.1419670672</v>
       </c>
       <c r="G3" s="19">
-        <v>0.28017456359102244</v>
+        <v>0.28182616330114135</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20183,7 +18446,7 @@
         <v>8440.537162162162</v>
       </c>
       <c r="G4" s="19">
-        <v>0.29526184538653366</v>
+        <v>0.2970023830427693</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20204,7 +18467,7 @@
         <v>39535.77777777778</v>
       </c>
       <c r="G5" s="19">
-        <v>0.011221945137157107</v>
+        <v>0.011288097328483633</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20225,7 +18488,7 @@
         <v>12999.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.025311720698254363</v>
+        <v>0.025460930640913083</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20246,7 +18509,7 @@
         <v>23797.18181818182</v>
       </c>
       <c r="G7" s="19">
-        <v>0.01371571072319202</v>
+        <v>0.013796563401479995</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20267,7 +18530,7 @@
         <v>7999.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.03778054862842893</v>
+        <v>0.03800326100589489</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20288,7 +18551,7 @@
         <v>9980.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.016084788029925186</v>
+        <v>0.01617960617082654</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20309,7 +18572,7 @@
         <v>5980.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.026558603491271822</v>
+        <v>0.026715163677411263</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20330,7 +18593,7 @@
         <v>10900.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.01371571072319202</v>
+        <v>0.013796563401479995</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20351,7 +18614,7 @@
         <v>12999.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.010473815461346634</v>
+        <v>0.010535557506584723</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20372,7 +18635,7 @@
         <v>6580.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.01658354114713217</v>
+        <v>0.016681299385425813</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20393,7 +18656,7 @@
         <v>18150.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.004488778054862843</v>
+        <v>0.004515238931393453</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20414,7 +18677,7 @@
         <v>14540.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.005486284289276808</v>
+        <v>0.005518625360591998</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20435,7 +18698,7 @@
         <v>4580.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.012967581047381545</v>
+        <v>0.013044023579581086</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20456,7 +18719,7 @@
         <v>17799.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.003117206982543641</v>
+        <v>0.0031355825912454532</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20477,236 +18740,133 @@
         <v>7580.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.003740648379052369</v>
+        <v>0.003762699109494544</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>IWA</t>
         </is>
       </c>
       <c r="B19" s="13">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="C19" s="13">
-        <v>193680</v>
+        <v>152985</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13">
-        <v>10193.684210526315</v>
+        <v>1645.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.002369077306733167</v>
+        <v>0.011664367239433086</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>IWA</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="B20" s="13">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C20" s="13">
-        <v>152985</v>
+        <v>133200</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13">
-        <v>1645.0</v>
+        <v>14800.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.011596009975062344</v>
+        <v>0.0011288097328483633</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>エコジー</t>
         </is>
       </c>
       <c r="B21" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="13">
-        <v>133200</v>
+        <v>72712</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13">
-        <v>14800.0</v>
+        <v>9089.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.0011221945137157108</v>
+        <v>0.0010033864291985452</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>エコジー</t>
+          <t>FEVORCS</t>
         </is>
       </c>
       <c r="B22" s="13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" s="13">
-        <v>72712</v>
+        <v>49000</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13">
-        <v>9089.0</v>
+        <v>9800.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.000997506234413965</v>
+        <v>0.0006271165182490907</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>FEVORCS</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="13">
-        <v>49000</v>
+        <v>34800</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13">
-        <v>9800.0</v>
+        <v>5800.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.0006234413965087282</v>
+        <v>0.0007525398218989088</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Joejoier</t>
+          <t>ノーブランド品</t>
         </is>
       </c>
       <c r="B24" s="13">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C24" s="13">
-        <v>37200</v>
+        <v>14900</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13">
-        <v>1488.0</v>
+        <v>14900.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.003117206982543641</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Hitachi</t>
-        </is>
-      </c>
-      <c r="B25" s="13">
-        <v>6</v>
-      </c>
-      <c r="C25" s="13">
-        <v>34800</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13">
-        <v>5800.0</v>
-      </c>
-      <c r="G25" s="19">
-        <v>0.0007481296758104738</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>ノーブランド品</t>
-        </is>
-      </c>
-      <c r="B26" s="13">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13">
-        <v>14900</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13">
-        <v>14900.0</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0.00012468827930174563</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Yizibuur</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <v>2</v>
-      </c>
-      <c r="C27" s="13">
-        <v>3176</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13">
-        <v>1588.0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0.00024937655860349125</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13">
-        <v>1180</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13">
-        <v>1180.0</v>
-      </c>
-      <c r="G28" s="19">
-        <v>0.00012468827930174563</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>pronala</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="19">
-        <v>0.0</v>
+        <v>0.00012542330364981815</v>
       </c>
     </row>
   </sheetData>
@@ -20717,7 +18877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -20781,7 +18941,7 @@
         <v>32200.0</v>
       </c>
       <c r="G2" s="19">
-        <v>0.19301745635910225</v>
+        <v>0.19415527404991847</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20802,7 +18962,7 @@
         <v>13183.1419670672</v>
       </c>
       <c r="G3" s="19">
-        <v>0.28017456359102244</v>
+        <v>0.28182616330114135</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20823,7 +18983,7 @@
         <v>8189.3067021748775</v>
       </c>
       <c r="G4" s="19">
-        <v>0.2809226932668329</v>
+        <v>0.2825787031230403</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20844,7 +19004,7 @@
         <v>39980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.00972568578553616</v>
+        <v>0.009783017684685815</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20865,7 +19025,7 @@
         <v>12999.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.025311720698254363</v>
+        <v>0.025460930640913083</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20886,7 +19046,7 @@
         <v>7999.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.03778054862842893</v>
+        <v>0.03800326100589489</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20907,7 +19067,7 @@
         <v>25392.103448275862</v>
       </c>
       <c r="G8" s="19">
-        <v>0.007231920199501247</v>
+        <v>0.007274551611689452</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20928,7 +19088,7 @@
         <v>9980.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.016084788029925186</v>
+        <v>0.01617960617082654</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20949,7 +19109,7 @@
         <v>5980.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.026558603491271822</v>
+        <v>0.026715163677411263</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20970,7 +19130,7 @@
         <v>10900.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.01371571072319202</v>
+        <v>0.013796563401479995</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20991,7 +19151,7 @@
         <v>8739.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.01683291770573566</v>
+        <v>0.01693214599272545</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21012,7 +19172,7 @@
         <v>22018.23076923077</v>
       </c>
       <c r="G13" s="19">
-        <v>0.006483790523690773</v>
+        <v>0.006522011789790543</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21033,7 +19193,7 @@
         <v>12999.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.010473815461346634</v>
+        <v>0.010535557506584723</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21054,7 +19214,7 @@
         <v>6580.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.01658354114713217</v>
+        <v>0.016681299385425813</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21075,7 +19235,7 @@
         <v>18150.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.004488778054862843</v>
+        <v>0.004515238931393453</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21096,7 +19256,7 @@
         <v>4580.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.012967581047381545</v>
+        <v>0.013044023579581086</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21117,7 +19277,7 @@
         <v>9680.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006109725685785536</v>
+        <v>0.006145741878841089</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21138,7 +19298,7 @@
         <v>17799.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.003117206982543641</v>
+        <v>0.0031355825912454532</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21159,7 +19319,7 @@
         <v>36648.333333333336</v>
       </c>
       <c r="G20" s="19">
-        <v>0.0014962593516209476</v>
+        <v>0.0015050796437978177</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21180,7 +19340,7 @@
         <v>18400.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.002743142144638404</v>
+        <v>0.002759312680295999</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21201,7 +19361,7 @@
         <v>21080.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.0022443890274314216</v>
+        <v>0.0022576194656967266</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21222,7 +19382,7 @@
         <v>11078.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.003491271820448878</v>
+        <v>0.003511852502194908</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21243,7 +19403,7 @@
         <v>9300.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.0038653366583541147</v>
+        <v>0.0038881224131443624</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21264,7 +19424,7 @@
         <v>7580.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.003740648379052369</v>
+        <v>0.003762699109494544</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21285,7 +19445,7 @@
         <v>6072.382352941177</v>
       </c>
       <c r="G26" s="19">
-        <v>0.004239401496259352</v>
+        <v>0.0042643923240938165</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21306,294 +19466,151 @@
         <v>14800.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.0011221945137157108</v>
+        <v>0.0011288097328483633</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Korin商店 古物商許可番号第801010002249号</t>
+          <t>Solesenyue</t>
         </is>
       </c>
       <c r="B28" s="13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C28" s="13">
-        <v>114000</v>
+        <v>72712</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13">
-        <v>38000.0</v>
+        <v>9089.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.0003740648379052369</v>
+        <v>0.0010033864291985452</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>OMITSU</t>
+          <t>Koda Electrical</t>
         </is>
       </c>
       <c r="B29" s="13">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C29" s="13">
-        <v>79680</v>
+        <v>49000</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13">
-        <v>4980.0</v>
+        <v>9800.0</v>
       </c>
       <c r="G29" s="19">
-        <v>0.00199501246882793</v>
+        <v>0.0006271165182490907</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Solesenyue</t>
+          <t>TSUGUMIオンラインショップ</t>
         </is>
       </c>
       <c r="B30" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="13">
-        <v>72712</v>
+        <v>48860</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13">
-        <v>9089.0</v>
+        <v>6980.0</v>
       </c>
       <c r="G30" s="19">
-        <v>0.000997506234413965</v>
+        <v>0.000877963125548727</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Koda Electrical</t>
+          <t>Pandora Garage</t>
         </is>
       </c>
       <c r="B31" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="13">
-        <v>49000</v>
+        <v>34800</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13">
-        <v>9800.0</v>
+        <v>5800.0</v>
       </c>
       <c r="G31" s="19">
-        <v>0.0006234413965087282</v>
+        <v>0.0007525398218989088</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>TSUGUMIオンラインショップ</t>
+          <t>junjun-store</t>
         </is>
       </c>
       <c r="B32" s="13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C32" s="13">
-        <v>48860</v>
+        <v>28000</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13">
-        <v>6980.0</v>
+        <v>14000.0</v>
       </c>
       <c r="G32" s="19">
-        <v>0.0008728179551122195</v>
+        <v>0.0002508466072996363</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Tan Peng Network Technology</t>
+          <t>JianShengTool</t>
         </is>
       </c>
       <c r="B33" s="13">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C33" s="13">
-        <v>37200</v>
+        <v>14900</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13">
-        <v>1488.0</v>
+        <v>14900.0</v>
       </c>
       <c r="G33" s="19">
-        <v>0.003117206982543641</v>
+        <v>0.00012542330364981815</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Pandora Garage</t>
+          <t>ダイユーエイト【「在庫あり」表示の商品は祝日も発送しております-土日は休みです-】</t>
         </is>
       </c>
       <c r="B34" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C34" s="13">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="13">
-        <v>5800.0</v>
-      </c>
+      <c r="F34" s="13"/>
       <c r="G34" s="19">
-        <v>0.0007481296758104738</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>junjun-store</t>
-        </is>
-      </c>
-      <c r="B35" s="13">
-        <v>2</v>
-      </c>
-      <c r="C35" s="13">
-        <v>28000</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13">
-        <v>14000.0</v>
-      </c>
-      <c r="G35" s="19">
-        <v>0.00024937655860349125</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>JianShengTool</t>
-        </is>
-      </c>
-      <c r="B36" s="13">
-        <v>1</v>
-      </c>
-      <c r="C36" s="13">
-        <v>14900</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13">
-        <v>14900.0</v>
-      </c>
-      <c r="G36" s="19">
-        <v>0.00012468827930174563</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>XiZou e-commerce(跟卖必下单投诉）</t>
-        </is>
-      </c>
-      <c r="B37" s="13">
-        <v>2</v>
-      </c>
-      <c r="C37" s="13">
-        <v>3176</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13">
-        <v>1588.0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0.00024937655860349125</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU（通常、5〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="B38" s="13">
-        <v>1</v>
-      </c>
-      <c r="C38" s="13">
-        <v>1180</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13">
-        <v>1180.0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0.00012468827930174563</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>gznllsmyxgs</t>
-        </is>
-      </c>
-      <c r="B39" s="13">
-        <v>0</v>
-      </c>
-      <c r="C39" s="13">
-        <v>0</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>ダイユーエイト【「在庫あり」表示の商品は祝日も発送しております-土日は休みです-】</t>
-        </is>
-      </c>
-      <c r="B40" s="13">
-        <v>0</v>
-      </c>
-      <c r="C40" s="13">
-        <v>0</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>配送3～11日以内PronalaShop-JP</t>
-        </is>
-      </c>
-      <c r="B41" s="13">
-        <v>0</v>
-      </c>
-      <c r="C41" s="13">
-        <v>0</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="19">
         <v>0.0</v>
       </c>
     </row>
